--- a/process/data/policy_review/gohsc-policy-indicator-checklist.xlsx
+++ b/process/data/policy_review/gohsc-policy-indicator-checklist.xlsx
@@ -10642,19 +10642,19 @@
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="65db695a-03c5-40dc-8b31-fde6e09a4b01">
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d026c80c-8c89-4d76-b5a4-adafffa27ea9">
       <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="b5388621-ea09-440d-99f9-2916c41d9c15" xsi:nil="true"/>
+    <TaxCatchAll xmlns="0f2f1471-5c80-47c6-b5fc-5f7f410df7a8" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A1151D2F3E73E54E96931DEC2C4BD52B" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="76f30d11f3f1ab636a1ce14ba6b65dba">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="65db695a-03c5-40dc-8b31-fde6e09a4b01" xmlns:ns3="b5388621-ea09-440d-99f9-2916c41d9c15" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ba8031a2bc0820f314467ad3bdd63355" ns2:_="" ns3:_="">
-    <xsd:import namespace="65db695a-03c5-40dc-8b31-fde6e09a4b01"/>
-    <xsd:import namespace="b5388621-ea09-440d-99f9-2916c41d9c15"/>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E46915CC77A6414794C0659BE0416FBE" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ce73daeef664d7c8d016e21b47135507">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="d026c80c-8c89-4d76-b5a4-adafffa27ea9" xmlns:ns3="0f2f1471-5c80-47c6-b5fc-5f7f410df7a8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="6117017243beacc659db0547db5dd191" ns2:_="" ns3:_="">
+    <xsd:import namespace="d026c80c-8c89-4d76-b5a4-adafffa27ea9"/>
+    <xsd:import namespace="0f2f1471-5c80-47c6-b5fc-5f7f410df7a8"/>
     <xsd:element name="properties">
       <xsd:complexType>
         <xsd:sequence>
@@ -10664,16 +10664,13 @@
                 <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
                 <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
                 <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceBillingMetadata" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -10681,7 +10678,7 @@
       </xsd:complexType>
     </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="65db695a-03c5-40dc-8b31-fde6e09a4b01" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="d026c80c-8c89-4d76-b5a4-adafffa27ea9" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
@@ -10699,60 +10696,45 @@
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="13b0b881-3bf5-4493-8d21-dd6cf614d6f8" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+    <xsd:element name="MediaServiceGenerationTime" ma:index="12" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="13" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="14" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="16" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="c921d02d-b337-4ce5-bd1c-22d9132a6b17" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
         </xsd:sequence>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="15" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="16" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+    <xsd:element name="MediaServiceOCR" ma:index="18" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
         </xsd:restriction>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="17" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="18" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="19" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="20" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceBillingMetadata" ma:index="21" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="b5388621-ea09-440d-99f9-2916c41d9c15" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="0f2f1471-5c80-47c6-b5fc-5f7f410df7a8" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="TaxCatchAll" ma:index="14" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{60c5b7ff-65dd-4b02-852f-dee59c90816d}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="b5388621-ea09-440d-99f9-2916c41d9c15">
+    <xsd:element name="TaxCatchAll" ma:index="17" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{3898acd8-9e76-4e3a-bd5c-f786070581b8}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="0f2f1471-5c80-47c6-b5fc-5f7f410df7a8">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:MultiChoiceLookup">
@@ -10884,22 +10866,7 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{79612192-7ECC-4289-942B-35AA1C3C498F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="65db695a-03c5-40dc-8b31-fde6e09a4b01"/>
-    <ds:schemaRef ds:uri="b5388621-ea09-440d-99f9-2916c41d9c15"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{47811B9A-0910-4A4B-8A04-79D2202DF82F}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
